--- a/research/v21-seeded-documents/packs/retail-price-accuracy/wa/documents/evidence-register.xlsx
+++ b/research/v21-seeded-documents/packs/retail-price-accuracy/wa/documents/evidence-register.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>checkout control gap mapped to Wash. Rev. Code § 19.94.230</t>
+          <t>checkout control gap mapped to Wash. Rev. Code § 19.94.390</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Wash. Rev. Code § 19.94.230</t>
+          <t>Wash. Rev. Code § 19.94.390</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://app.leg.wa.gov/RCW/default.aspx?cite=19.94.230</t>
+          <t>https://app.leg.wa.gov/RCW/default.aspx?cite=19.94.390</t>
         </is>
       </c>
     </row>
